--- a/DATA/Processed/armax_selected_results.xlsx
+++ b/DATA/Processed/armax_selected_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,7 +464,37 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>hqic</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>loglik</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>resid_mean</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>resid_std</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ljungbox_p_12</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ljungbox_p_24</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>converged</t>
         </is>
       </c>
     </row>
@@ -476,36 +506,54 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ARMAX(1,0)</t>
+          <t>ARIMA(1,0,1) + exog</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>dlog_exr_L1, dlog_res_L5</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>d_str_L3 (p=0.976), dlog_m2_L4 (p=0.867), d_ltr_L4 (p=0.883), dlog_res_L3 (p=0.838), d_ltr_L1 (p=0.799), d_ltr_L2 (p=0.771), d_str_L5 (p=0.705), d_ltr_L6 (p=0.703), dlog_res_L1 (p=0.716), d_ltr_L5 (p=0.596), d_str_L1 (p=0.660), d_str_L2 (p=0.514), d_str_L6 (p=0.566), dlog_res_L2 (p=0.557), dlog_m2_L6 (p=0.568), dlog_m2_L5 (p=0.329), dlog_exr_L5 (p=0.324), d_ltr_L3 (p=0.274), dlog_exr_L4 (p=0.312), dlog_res_L4 (p=0.335), dlog_m2_L2 (p=0.259), d_str_L4 (p=0.318), dlog_exr_L3 (p=0.172), dlog_m2_L3 (p=0.152), dlog_res_L6 (p=0.157), dlog_exr_L2 (p=0.202), dlog_m2_L1 (p=0.256), dlog_exr_L6 (p=0.137)</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0003934946331772469</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-909.286019580021</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-892.8164268098416</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-902.6010940423733</v>
+      </c>
+      <c r="K2" t="n">
+        <v>460.6430097900105</v>
+      </c>
+      <c r="L2" t="n">
+        <v>4.209536866967894e-06</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.004426323076289586</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.376971215172562</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.04439467720905674</v>
+      </c>
+      <c r="P2" t="b">
         <v>1</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>dlog_res_L5</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>dlog_exr_L8 (p=0.997), d_ltr_L2 (p=0.967), d_str_L6 (p=0.976), dlog_res_L1 (p=0.994), d_ltr_L5 (p=0.983), dlog_exr_L4 (p=0.967), dlog_m2_L12 (p=0.975), d_ltr_L7 (p=0.941), dlog_m2_L1 (p=0.893), d_str_L12 (p=0.940), d_ltr_L3 (p=0.799), d_ltr_L1 (p=0.775), dlog_res_L12 (p=0.771), dlog_m2_L4 (p=0.754), dlog_m2_L9 (p=0.768), dlog_res_L10 (p=0.794), d_ltr_L4 (p=0.749), d_str_L11 (p=0.717), d_ltr_L6 (p=0.735), dlog_exr_L3 (p=0.725), dlog_exr_L11 (p=0.716), d_str_L3 (p=0.591), dlog_exr_L12 (p=0.668), dlog_m2_L8 (p=0.630), d_ltr_L8 (p=0.548), dlog_res_L8 (p=0.567), dlog_exr_L7 (p=0.570), dlog_exr_L10 (p=0.546), d_str_L1 (p=0.456), dlog_exr_L9 (p=0.459), dlog_m2_L5 (p=0.422), d_str_L2 (p=0.442), dlog_m2_L10 (p=0.403), dlog_res_L4 (p=0.503), dlog_m2_L6 (p=0.450), d_str_L5 (p=0.452), dlog_m2_L11 (p=0.345), dlog_exr_L5 (p=0.325), dlog_m2_L3 (p=0.218), d_str_L4 (p=0.358), dlog_res_L2 (p=0.196), d_ltr_L9 (p=0.142), dlog_res_L9 (p=0.233), dlog_res_L7 (p=0.216), d_str_L9 (p=0.225), dlog_res_L6 (p=0.130), dlog_exr_L6 (p=0.207), dlog_m2_L2 (p=0.227), d_str_L7 (p=0.171), d_ltr_L10 (p=0.125), d_str_L10 (p=0.194), dlog_m2_L7 (p=0.138), dlog_res_L3 (p=0.111), d_str_L8 (p=0.138), d_ltr_L12 (p=0.230), dlog_exr_L2 (p=0.350), dlog_res_L11 (p=0.206), d_ltr_L11 (p=0.266), dlog_exr_L1 (p=0.145)</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>0.000618653483079547</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-855.8583938754496</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-845.093002346533</v>
-      </c>
-      <c r="J2" t="n">
-        <v>431.9291969377248</v>
       </c>
     </row>
     <row r="3">
@@ -516,36 +564,54 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ARMAX(1,1)</t>
+          <t>ARIMA(1,0,1) + exog</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>dlog_m2_L8, dlog_exr_L7, dlog_res_L8, dlog_res_L10, dlog_res_L12, d_str_L10, d_str_L11</t>
+          <t>dlog_exr_L1, dlog_exr_L6, d_str_L3, d_str_L4</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>dlog_m2_L11 (p=0.997), d_str_L4 (p=0.993), d_str_L12 (p=0.945), d_ltr_L3 (p=0.942), d_ltr_L5 (p=0.935), dlog_exr_L4 (p=0.936), dlog_exr_L11 (p=0.915), dlog_res_L2 (p=0.921), dlog_exr_L2 (p=0.929), d_ltr_L8 (p=0.860), dlog_m2_L9 (p=0.876), dlog_m2_L2 (p=0.852), d_str_L5 (p=0.818), d_str_L1 (p=0.733), d_str_L8 (p=0.772), dlog_m2_L6 (p=0.847), d_str_L6 (p=0.677), dlog_m2_L12 (p=0.778), dlog_m2_L7 (p=0.663), dlog_exr_L6 (p=0.625), dlog_res_L9 (p=0.648), dlog_res_L5 (p=0.587), d_ltr_L2 (p=0.512), dlog_exr_L3 (p=0.445), d_ltr_L1 (p=0.553), dlog_m2_L10 (p=0.607), d_str_L2 (p=0.563), d_str_L7 (p=0.530), dlog_m2_L3 (p=0.352), dlog_res_L11 (p=0.257), d_ltr_L11 (p=0.298), dlog_res_L1 (p=0.334), dlog_m2_L4 (p=0.287), dlog_m2_L1 (p=0.315), dlog_exr_L8 (p=0.261), dlog_exr_L9 (p=0.473), d_ltr_L6 (p=0.214), dlog_res_L6 (p=0.278), dlog_res_L7 (p=0.330), d_str_L9 (p=0.240), d_ltr_L9 (p=0.414), dlog_exr_L10 (p=0.260), dlog_exr_L12 (p=0.278), d_ltr_L4 (p=0.289), dlog_res_L4 (p=0.464), dlog_m2_L5 (p=0.429), dlog_res_L3 (p=0.262), d_str_L3 (p=0.305), d_ltr_L12 (p=0.140), d_ltr_L10 (p=0.294), dlog_exr_L1 (p=0.299), dlog_exr_L5 (p=0.129), d_ltr_L7 (p=0.210)</t>
+          <t>dlog_res_L5 (p=0.990), dlog_m2_L3 (p=0.975), dlog_res_L6 (p=0.965), d_ltr_L5 (p=0.944), dlog_m2_L2 (p=0.940), d_ltr_L4 (p=0.822), dlog_exr_L4 (p=0.780), dlog_res_L4 (p=0.646), dlog_m2_L5 (p=0.679), dlog_m2_L4 (p=0.658), dlog_exr_L2 (p=0.664), dlog_res_L2 (p=0.659), d_str_L1 (p=0.646), dlog_res_L3 (p=0.570), dlog_exr_L3 (p=0.592), dlog_m2_L1 (p=0.580), dlog_exr_L5 (p=0.645), d_ltr_L1 (p=0.466), dlog_res_L1 (p=0.503), d_str_L6 (p=0.477), dlog_m2_L6 (p=0.343), d_str_L2 (p=0.393), d_ltr_L2 (p=0.277), d_ltr_L6 (p=0.249), d_ltr_L3 (p=0.229), d_str_L5 (p=0.502)</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.0011237883162718</v>
+        <v>0.00132618044008491</v>
       </c>
       <c r="H3" t="n">
-        <v>-957.328230200416</v>
+        <v>-996.3783710459379</v>
       </c>
       <c r="I3" t="n">
-        <v>-929.5885558528765</v>
+        <v>-975.6986312165733</v>
       </c>
       <c r="J3" t="n">
-        <v>489.664115100208</v>
+        <v>-988.0138428427418</v>
+      </c>
+      <c r="K3" t="n">
+        <v>506.189185522969</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.035820610851071e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.001390002871780071</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.5363225489606351</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.5250418324547326</v>
+      </c>
+      <c r="P3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -556,36 +622,54 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ARMAX(1,0)</t>
+          <t>ARIMA(1,0,0) + exog</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>dlog_m2_L6, dlog_m2_L9, dlog_exr_L5, dlog_exr_L11, dlog_res_L4, dlog_res_L8, dlog_res_L11, dlog_res_L12, d_ltr_L1, d_ltr_L2, d_ltr_L4, d_ltr_L8, d_ltr_L10, d_str_L2, d_str_L3, d_str_L4, d_str_L10</t>
+          <t>dlog_exr_L5, d_ltr_L1, d_ltr_L2, d_str_L3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>dlog_exr_L6 (p=0.999), d_str_L9 (p=0.983), d_ltr_L12 (p=0.979), dlog_exr_L10 (p=0.975), d_str_L5 (p=0.961), d_str_L1 (p=0.957), d_ltr_L9 (p=0.951), d_ltr_L6 (p=0.950), dlog_m2_L5 (p=0.938), d_ltr_L3 (p=0.898), dlog_m2_L3 (p=0.824), dlog_res_L5 (p=0.863), dlog_exr_L4 (p=0.821), dlog_exr_L12 (p=0.789), dlog_res_L7 (p=0.790), d_ltr_L11 (p=0.764), dlog_exr_L9 (p=0.785), dlog_exr_L2 (p=0.745), d_str_L12 (p=0.700), d_str_L8 (p=0.740), dlog_m2_L7 (p=0.744), d_str_L11 (p=0.681), dlog_m2_L4 (p=0.669), dlog_exr_L1 (p=0.612), d_str_L7 (p=0.573), dlog_res_L2 (p=0.559), d_ltr_L7 (p=0.555), dlog_m2_L12 (p=0.656), dlog_exr_L3 (p=0.510), dlog_res_L3 (p=0.456), dlog_m2_L1 (p=0.540), d_str_L6 (p=0.424), dlog_res_L6 (p=0.300), dlog_m2_L8 (p=0.316), dlog_m2_L11 (p=0.330), dlog_res_L1 (p=0.257), dlog_res_L10 (p=0.245), dlog_m2_L2 (p=0.303), dlog_res_L9 (p=0.357), dlog_m2_L10 (p=0.362), dlog_exr_L7 (p=0.317), dlog_exr_L8 (p=0.395), d_ltr_L5 (p=0.311)</t>
+          <t>dlog_res_L2 (p=0.984), dlog_exr_L3 (p=0.963), dlog_m2_L4 (p=0.914), dlog_res_L5 (p=0.875), dlog_m2_L5 (p=0.833), dlog_exr_L6 (p=0.765), d_str_L2 (p=0.793), dlog_m2_L3 (p=0.658), d_ltr_L3 (p=0.638), dlog_exr_L1 (p=0.628), d_ltr_L6 (p=0.589), d_str_L4 (p=0.694), dlog_exr_L2 (p=0.562), dlog_res_L3 (p=0.636), dlog_m2_L1 (p=0.541), dlog_res_L4 (p=0.371), dlog_res_L6 (p=0.379), d_str_L6 (p=0.363), dlog_m2_L6 (p=0.416), dlog_res_L1 (p=0.335), dlog_m2_L2 (p=0.224), d_ltr_L4 (p=0.216), d_ltr_L5 (p=0.315), d_str_L5 (p=0.187), dlog_exr_L4 (p=0.216), d_str_L1 (p=0.143)</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.0001838022252582326</v>
+        <v>0.000716444248768332</v>
       </c>
       <c r="H4" t="n">
-        <v>-1158.295076216546</v>
+        <v>-1212.235743227406</v>
       </c>
       <c r="I4" t="n">
-        <v>-1104.468118571963</v>
+        <v>-1193.021218328863</v>
       </c>
       <c r="J4" t="n">
-        <v>599.1475381082731</v>
+        <v>-1204.436663433484</v>
+      </c>
+      <c r="K4" t="n">
+        <v>613.117871613703</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.800635324134844e-06</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.00117549300634616</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.6999205575225076</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.5708857402197465</v>
+      </c>
+      <c r="P4" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -596,36 +680,54 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ARMAX(1,0)</t>
+          <t>ARIMA(1,0,1) + exog</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>dlog_m2_L9, dlog_m2_L11, dlog_exr_L8, d_ltr_L4, d_ltr_L5, d_str_L12</t>
+          <t>d_ltr_L4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>dlog_res_L8 (p=0.996), dlog_res_L4 (p=0.949), d_str_L7 (p=0.937), d_ltr_L12 (p=0.920), d_str_L9 (p=0.877), d_ltr_L9 (p=0.896), dlog_m2_L10 (p=0.862), dlog_res_L12 (p=0.848), dlog_exr_L6 (p=0.850), dlog_m2_L7 (p=0.791), dlog_m2_L8 (p=0.808), d_str_L1 (p=0.755), d_ltr_L1 (p=0.818), d_ltr_L6 (p=0.748), dlog_res_L5 (p=0.652), d_ltr_L10 (p=0.631), dlog_res_L9 (p=0.548), dlog_exr_L7 (p=0.559), dlog_exr_L9 (p=0.695), dlog_exr_L2 (p=0.655), d_ltr_L7 (p=0.569), dlog_m2_L3 (p=0.626), dlog_m2_L4 (p=0.497), dlog_exr_L1 (p=0.441), dlog_res_L1 (p=0.554), dlog_exr_L3 (p=0.340), dlog_res_L6 (p=0.430), d_str_L8 (p=0.404), dlog_exr_L10 (p=0.516), d_str_L4 (p=0.510), d_str_L5 (p=0.744), d_str_L6 (p=0.573), d_str_L3 (p=0.502), dlog_exr_L12 (p=0.534), d_str_L11 (p=0.535), d_str_L10 (p=0.453), d_ltr_L3 (p=0.411), dlog_res_L3 (p=0.304), d_ltr_L8 (p=0.334), dlog_exr_L11 (p=0.199), dlog_m2_L2 (p=0.163), dlog_m2_L6 (p=0.179), d_ltr_L11 (p=0.182), dlog_res_L11 (p=0.178), dlog_m2_L1 (p=0.192), dlog_res_L2 (p=0.199), dlog_res_L10 (p=0.139), dlog_res_L7 (p=0.155), d_str_L2 (p=0.115), d_ltr_L2 (p=0.147), dlog_exr_L4 (p=0.199), dlog_m2_L5 (p=0.157), dlog_exr_L5 (p=0.168), dlog_m2_L12 (p=0.239)</t>
+          <t>d_str_L4 (p=0.915), d_ltr_L3 (p=0.909), dlog_res_L4 (p=0.970), dlog_res_L3 (p=0.946), dlog_exr_L1 (p=0.895), dlog_exr_L6 (p=0.868), d_str_L3 (p=0.913), d_str_L2 (p=0.982), dlog_res_L5 (p=0.670), d_str_L5 (p=0.790), d_str_L6 (p=0.781), dlog_exr_L3 (p=0.817), dlog_m2_L3 (p=0.976), dlog_exr_L5 (p=0.621), d_ltr_L5 (p=0.722), dlog_m2_L6 (p=0.520), dlog_m2_L5 (p=0.447), dlog_exr_L2 (p=0.424), dlog_res_L6 (p=0.837), dlog_m2_L2 (p=0.492), d_ltr_L6 (p=0.286), dlog_res_L2 (p=0.697), dlog_m2_L1 (p=0.376), dlog_m2_L4 (p=0.324), dlog_res_L1 (p=0.340), d_ltr_L1 (p=0.470), d_ltr_L2 (p=0.239), d_str_L1 (p=0.325), dlog_exr_L4 (p=0.113)</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.001086368664994677</v>
+        <v>0.00103391778732475</v>
       </c>
       <c r="H5" t="n">
-        <v>-1144.528238440368</v>
+        <v>-1195.263138451749</v>
       </c>
       <c r="I5" t="n">
-        <v>-1120.306107500306</v>
+        <v>-1181.538477809933</v>
       </c>
       <c r="J5" t="n">
-        <v>581.2641192201839</v>
+        <v>-1189.692367170376</v>
+      </c>
+      <c r="K5" t="n">
+        <v>602.6315692258746</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3.001464122511654e-06</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.001287678627996775</v>
+      </c>
+      <c r="N5" t="n">
+        <v>8.988201321175238e-05</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.421042371661852e-05</v>
+      </c>
+      <c r="P5" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/DATA/Processed/armax_selected_results.xlsx
+++ b/DATA/Processed/armax_selected_results.xlsx
@@ -680,51 +680,51 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ARIMA(1,0,1) + exog</t>
+          <t>ARIMA(2,0,1) + exog</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>115</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>d_ltr_L4</t>
+          <t>dlog_m2_L1, d_ltr_L4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>d_str_L4 (p=0.915), d_ltr_L3 (p=0.909), dlog_res_L4 (p=0.970), dlog_res_L3 (p=0.946), dlog_exr_L1 (p=0.895), dlog_exr_L6 (p=0.868), d_str_L3 (p=0.913), d_str_L2 (p=0.982), dlog_res_L5 (p=0.670), d_str_L5 (p=0.790), d_str_L6 (p=0.781), dlog_exr_L3 (p=0.817), dlog_m2_L3 (p=0.976), dlog_exr_L5 (p=0.621), d_ltr_L5 (p=0.722), dlog_m2_L6 (p=0.520), dlog_m2_L5 (p=0.447), dlog_exr_L2 (p=0.424), dlog_res_L6 (p=0.837), dlog_m2_L2 (p=0.492), d_ltr_L6 (p=0.286), dlog_res_L2 (p=0.697), dlog_m2_L1 (p=0.376), dlog_m2_L4 (p=0.324), dlog_res_L1 (p=0.340), d_ltr_L1 (p=0.470), d_ltr_L2 (p=0.239), d_str_L1 (p=0.325), dlog_exr_L4 (p=0.113)</t>
+          <t>d_ltr_L3 (p=0.985), dlog_exr_L6 (p=0.989), d_str_L1 (p=0.975), dlog_res_L3 (p=0.898), dlog_m2_L3 (p=0.877), d_str_L4 (p=0.873), dlog_exr_L1 (p=0.951), d_ltr_L5 (p=0.597), dlog_m2_L4 (p=0.593), dlog_m2_L6 (p=0.557), dlog_m2_L5 (p=0.492), d_str_L6 (p=0.562), d_str_L3 (p=0.600), dlog_res_L4 (p=0.972), d_str_L5 (p=0.681), dlog_res_L6 (p=0.532), dlog_exr_L3 (p=0.631), dlog_exr_L5 (p=0.620), dlog_res_L5 (p=0.475), dlog_exr_L2 (p=0.571), dlog_m2_L2 (p=0.697), d_str_L2 (p=0.316), d_ltr_L6 (p=0.442), d_ltr_L1 (p=0.212), dlog_res_L1 (p=0.546), dlog_res_L2 (p=0.187), d_ltr_L2 (p=0.331), dlog_exr_L4 (p=0.120)</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.00103391778732475</v>
+        <v>0.0009057217898672527</v>
       </c>
       <c r="H5" t="n">
-        <v>-1195.263138451749</v>
+        <v>-1202.575439001582</v>
       </c>
       <c r="I5" t="n">
-        <v>-1181.538477809933</v>
+        <v>-1183.360914103039</v>
       </c>
       <c r="J5" t="n">
-        <v>-1189.692367170376</v>
+        <v>-1194.77635920766</v>
       </c>
       <c r="K5" t="n">
-        <v>602.6315692258746</v>
+        <v>608.287719500791</v>
       </c>
       <c r="L5" t="n">
-        <v>3.001464122511654e-06</v>
+        <v>2.782197519015903e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001287678627996775</v>
+        <v>0.001224780420563335</v>
       </c>
       <c r="N5" t="n">
-        <v>8.988201321175238e-05</v>
+        <v>0.01323673943680844</v>
       </c>
       <c r="O5" t="n">
-        <v>2.421042371661852e-05</v>
+        <v>0.0129995182620248</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>

--- a/DATA/Processed/armax_selected_results.xlsx
+++ b/DATA/Processed/armax_selected_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,50 +449,55 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>outlier_dates</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>const</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>aic</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>bic</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>hqic</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>loglik</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>resid_mean</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>resid_std</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>ljungbox_p_12</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>ljungbox_p_24</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>converged</t>
         </is>
@@ -513,47 +518,52 @@
         <v>115</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>dlog_exr_L1, dlog_res_L5</t>
+          <t>dlog_m2_L2, dlog_m2_L3, dlog_m2_L5, dlog_exr_L5, d_str_L2, thailand_outlier_1, thailand_outlier_2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>d_str_L3 (p=0.976), dlog_m2_L4 (p=0.867), d_ltr_L4 (p=0.883), dlog_res_L3 (p=0.838), d_ltr_L1 (p=0.799), d_ltr_L2 (p=0.771), d_str_L5 (p=0.705), d_ltr_L6 (p=0.703), dlog_res_L1 (p=0.716), d_ltr_L5 (p=0.596), d_str_L1 (p=0.660), d_str_L2 (p=0.514), d_str_L6 (p=0.566), dlog_res_L2 (p=0.557), dlog_m2_L6 (p=0.568), dlog_m2_L5 (p=0.329), dlog_exr_L5 (p=0.324), d_ltr_L3 (p=0.274), dlog_exr_L4 (p=0.312), dlog_res_L4 (p=0.335), dlog_m2_L2 (p=0.259), d_str_L4 (p=0.318), dlog_exr_L3 (p=0.172), dlog_m2_L3 (p=0.152), dlog_res_L6 (p=0.157), dlog_exr_L2 (p=0.202), dlog_m2_L1 (p=0.256), dlog_exr_L6 (p=0.137)</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>0.0003934946331772469</v>
+          <t>dlog_res_L6 (p=0.947), d_ltr_L4 (p=0.978), d_ltr_L5 (p=0.936), d_str_L1 (p=0.795), d_ltr_L3 (p=0.985), dlog_res_L3 (p=0.965), dlog_exr_L1 (p=0.930), d_ltr_L6 (p=0.905), dlog_res_L5 (p=0.777), d_str_L6 (p=0.798), dlog_m2_L1 (p=0.883), dlog_res_L4 (p=0.960), d_str_L5 (p=0.764), dlog_res_L2 (p=0.767), d_ltr_L2 (p=0.690), d_str_L3 (p=0.613), d_str_L4 (p=0.512), dlog_res_L1 (p=0.557), dlog_exr_L3 (p=0.495), dlog_exr_L4 (p=0.491), dlog_exr_L2 (p=0.284), dlog_m2_L4 (p=0.229), dlog_exr_L6 (p=0.202), d_ltr_L1 (p=0.111), dlog_m2_L6 (p=0.139)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2022-01-01, 2023-02-01</t>
+        </is>
       </c>
       <c r="H2" t="n">
-        <v>-909.286019580021</v>
+        <v>-0.0009896659438369713</v>
       </c>
       <c r="I2" t="n">
-        <v>-892.8164268098416</v>
+        <v>-1088.655529865743</v>
       </c>
       <c r="J2" t="n">
-        <v>-902.6010940423733</v>
+        <v>-1058.461276453747</v>
       </c>
       <c r="K2" t="n">
-        <v>460.6430097900105</v>
+        <v>-1076.399833046722</v>
       </c>
       <c r="L2" t="n">
-        <v>4.209536866967894e-06</v>
+        <v>555.3277649328714</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004426323076289586</v>
+        <v>2.230771599969086e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>0.376971215172562</v>
+        <v>0.001941998513236662</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04439467720905674</v>
-      </c>
-      <c r="P2" t="b">
-        <v>1</v>
+        <v>0.6492189108346722</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.6232403986831121</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -583,34 +593,35 @@
           <t>dlog_res_L5 (p=0.990), dlog_m2_L3 (p=0.975), dlog_res_L6 (p=0.965), d_ltr_L5 (p=0.944), dlog_m2_L2 (p=0.940), d_ltr_L4 (p=0.822), dlog_exr_L4 (p=0.780), dlog_res_L4 (p=0.646), dlog_m2_L5 (p=0.679), dlog_m2_L4 (p=0.658), dlog_exr_L2 (p=0.664), dlog_res_L2 (p=0.659), d_str_L1 (p=0.646), dlog_res_L3 (p=0.570), dlog_exr_L3 (p=0.592), dlog_m2_L1 (p=0.580), dlog_exr_L5 (p=0.645), d_ltr_L1 (p=0.466), dlog_res_L1 (p=0.503), d_str_L6 (p=0.477), dlog_m2_L6 (p=0.343), d_str_L2 (p=0.393), d_ltr_L2 (p=0.277), d_ltr_L6 (p=0.249), d_ltr_L3 (p=0.229), d_str_L5 (p=0.502)</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
         <v>0.00132618044008491</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>-996.3783710459379</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>-975.6986312165733</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>-988.0138428427418</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>506.189185522969</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>1.035820610851071e-05</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>0.001390002871780071</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>0.5363225489606351</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>0.5250418324547326</v>
       </c>
-      <c r="P3" t="b">
+      <c r="Q3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -641,34 +652,35 @@
           <t>dlog_res_L2 (p=0.984), dlog_exr_L3 (p=0.963), dlog_m2_L4 (p=0.914), dlog_res_L5 (p=0.875), dlog_m2_L5 (p=0.833), dlog_exr_L6 (p=0.765), d_str_L2 (p=0.793), dlog_m2_L3 (p=0.658), d_ltr_L3 (p=0.638), dlog_exr_L1 (p=0.628), d_ltr_L6 (p=0.589), d_str_L4 (p=0.694), dlog_exr_L2 (p=0.562), dlog_res_L3 (p=0.636), dlog_m2_L1 (p=0.541), dlog_res_L4 (p=0.371), dlog_res_L6 (p=0.379), d_str_L6 (p=0.363), dlog_m2_L6 (p=0.416), dlog_res_L1 (p=0.335), dlog_m2_L2 (p=0.224), d_ltr_L4 (p=0.216), d_ltr_L5 (p=0.315), d_str_L5 (p=0.187), dlog_exr_L4 (p=0.216), d_str_L1 (p=0.143)</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
         <v>0.000716444248768332</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>-1212.235743227406</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>-1193.021218328863</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>-1204.436663433484</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>613.117871613703</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>1.800635324134844e-06</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>0.00117549300634616</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>0.6999205575225076</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>0.5708857402197465</v>
       </c>
-      <c r="P4" t="b">
+      <c r="Q4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -696,37 +708,38 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>d_ltr_L3 (p=0.985), dlog_exr_L6 (p=0.989), d_str_L1 (p=0.975), dlog_res_L3 (p=0.898), dlog_m2_L3 (p=0.877), d_str_L4 (p=0.873), dlog_exr_L1 (p=0.951), d_ltr_L5 (p=0.597), dlog_m2_L4 (p=0.593), dlog_m2_L6 (p=0.557), dlog_m2_L5 (p=0.492), d_str_L6 (p=0.562), d_str_L3 (p=0.600), dlog_res_L4 (p=0.972), d_str_L5 (p=0.681), dlog_res_L6 (p=0.532), dlog_exr_L3 (p=0.631), dlog_exr_L5 (p=0.620), dlog_res_L5 (p=0.475), dlog_exr_L2 (p=0.571), dlog_m2_L2 (p=0.697), d_str_L2 (p=0.316), d_ltr_L6 (p=0.442), d_ltr_L1 (p=0.212), dlog_res_L1 (p=0.546), dlog_res_L2 (p=0.187), d_ltr_L2 (p=0.331), dlog_exr_L4 (p=0.120)</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
+          <t>d_ltr_L3 (p=0.985), dlog_exr_L6 (p=0.989), d_str_L1 (p=0.975), dlog_res_L3 (p=0.898), dlog_m2_L3 (p=0.877), d_str_L4 (p=0.873), dlog_exr_L1 (p=0.951), d_ltr_L5 (p=0.597), dlog_m2_L4 (p=0.593), dlog_m2_L6 (p=0.557), dlog_m2_L5 (p=0.492), d_str_L6 (p=0.562), d_str_L3 (p=0.575), dlog_res_L4 (p=0.972), d_str_L5 (p=0.681), dlog_res_L6 (p=0.532), dlog_exr_L3 (p=0.631), dlog_exr_L5 (p=0.620), dlog_res_L5 (p=0.475), dlog_exr_L2 (p=0.571), dlog_m2_L2 (p=0.697), d_str_L2 (p=0.316), d_ltr_L6 (p=0.442), d_ltr_L1 (p=0.212), dlog_res_L1 (p=0.546), dlog_res_L2 (p=0.187), d_ltr_L2 (p=0.331), dlog_exr_L4 (p=0.120)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
         <v>0.0009057217898672527</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>-1202.575439001582</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>-1183.360914103039</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>-1194.77635920766</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>608.287719500791</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>2.782197519015903e-06</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>0.001224780420563335</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>0.01323673943680844</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>0.0129995182620248</v>
       </c>
-      <c r="P5" t="b">
+      <c r="Q5" t="b">
         <v>1</v>
       </c>
     </row>
